--- a/output/xlsx/ListarUsuarios--GT-.xlsx
+++ b/output/xlsx/ListarUsuarios--GT-.xlsx
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Precondition: </t>
   </si>
   <si>
-    <t>Existem diversos usuarios de diferentes perfis cadastrados no sistema</t>
+    <t>Existem diversos usuários de diferentes perfis cadastrados no sistema</t>
   </si>
   <si>
     <t>#</t>
@@ -107,10 +107,10 @@
     <t>exibe lista com todos os usuários cadastrados</t>
   </si>
   <si>
-    <t>system: SYSTEM: exibe pagina contendo os campos 'Name', 'Login', 'Type' e 'Language' devidamente preenchidos</t>
-  </si>
-  <si>
-    <t>exibe pagina contendo os campos 'Name', 'Login', 'Type' e 'Language' devidamente preenchidos</t>
+    <t>system: SYSTEM: exibe página contendo os campos 'Name', 'Login', 'Type' e 'Language' devidamente preenchidos</t>
+  </si>
+  <si>
+    <t>exibe página contendo os campos 'Name', 'Login', 'Type' e 'Language' devidamente preenchidos</t>
   </si>
   <si>
     <t xml:space="preserve">Postcondition: </t>
@@ -122,10 +122,10 @@
     <t>Alternative Flow 1: Gerente</t>
   </si>
   <si>
-    <t>system: SYSTEM: exibe lista somente cos usuários cadastrados do tipo 'Operator' associados ao mesmo laboratorio que o gerente</t>
-  </si>
-  <si>
-    <t>exibe lista somente cos usuários cadastrados do tipo 'Operator' associados ao mesmo laboratorio que o gerente</t>
+    <t>system: SYSTEM: exibe lista somente cos usuários cadastrados do tipo 'Operator' associados ao mesmo laboratório que o gerente</t>
+  </si>
+  <si>
+    <t>exibe lista somente cos usuários cadastrados do tipo 'Operator' associados ao mesmo laboratório que o gerente</t>
   </si>
   <si>
     <t>TC3</t>
@@ -134,10 +134,10 @@
     <t>Alternative Flow 2: administrador</t>
   </si>
   <si>
-    <t>system: SYSTEM: exibe lista somente cos usuarios cadastrados do tipo 'Operator' e 'Manager' associados ao mesmo laboratorio que o administrador</t>
-  </si>
-  <si>
-    <t>exibe lista somente cos usuarios cadastrados do tipo 'Operator' e 'Manager' associados ao mesmo laboratorio que o administrador</t>
+    <t>system: SYSTEM: exibe lista somente cos usuários cadastrados do tipo 'Operator' e 'Manager' associados ao mesmo laboratório que o administrador</t>
+  </si>
+  <si>
+    <t>exibe lista somente cos usuários cadastrados do tipo 'Operator' e 'Manager' associados ao mesmo laboratório que o administrador</t>
   </si>
 </sst>
 </file>
